--- a/results/canaliculi/543-2/all_method_results/measurements_cap275.xlsx
+++ b/results/canaliculi/543-2/all_method_results/measurements_cap275.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,84 +488,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>roots_count: threads leaving the lacuna surface (ownership-free). ring_length_r&lt;R&gt;_px: skeleton px within R px of the body, nearest lacuna only (ownership-free). owned_length_px: sum of owned edge lengths (changes with the reach cap).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>56.5833</v>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="n">
-        <v>36.6419</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>12</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>total_length_px</t>
+          <t>canaliculi_count</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1518.0344</v>
+        <v>56.5833</v>
       </c>
       <c r="C8" t="n">
-        <v>1219.1671</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>1023.8176</v>
+        <v>36.6419</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -575,24 +558,144 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1518.0344</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1219.1671</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1023.8176</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>27.2699</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>27.6455</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>4.1205</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7.5833</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7455</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>306.5833</v>
+      </c>
+      <c r="C12" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>89.1673</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>966.4167</v>
+      </c>
+      <c r="C13" t="n">
+        <v>929.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>189.5389</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1518.0344</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1219.1671</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1023.8176</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -807,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,10 +936,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>on_border</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>units</t>
         </is>
@@ -855,10 +978,22 @@
       <c r="D2" t="n">
         <v>22.1308</v>
       </c>
-      <c r="E2" t="b">
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>366</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1178</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1615.5454</v>
+      </c>
+      <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -877,10 +1012,22 @@
       <c r="D3" t="n">
         <v>25.5712</v>
       </c>
-      <c r="E3" t="b">
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>510</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1353</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3273.1181</v>
+      </c>
+      <c r="I3" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -899,10 +1046,22 @@
       <c r="D4" t="n">
         <v>28.8414</v>
       </c>
-      <c r="E4" t="b">
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>316</v>
+      </c>
+      <c r="G4" t="n">
+        <v>919</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1009.4478</v>
+      </c>
+      <c r="I4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -921,10 +1080,22 @@
       <c r="D5" t="n">
         <v>19.5402</v>
       </c>
-      <c r="E5" t="b">
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>305</v>
+      </c>
+      <c r="G5" t="n">
+        <v>695</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1016.0925</v>
+      </c>
+      <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -943,10 +1114,22 @@
       <c r="D6" t="n">
         <v>28.2779</v>
       </c>
-      <c r="E6" t="b">
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>256</v>
+      </c>
+      <c r="G6" t="n">
+        <v>826</v>
+      </c>
+      <c r="H6" t="n">
+        <v>509.0021</v>
+      </c>
+      <c r="I6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -965,10 +1148,22 @@
       <c r="D7" t="n">
         <v>29.63</v>
       </c>
-      <c r="E7" t="b">
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>314</v>
+      </c>
+      <c r="G7" t="n">
+        <v>898</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1422.2418</v>
+      </c>
+      <c r="I7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -987,10 +1182,22 @@
       <c r="D8" t="n">
         <v>35.2664</v>
       </c>
-      <c r="E8" t="b">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>136</v>
+      </c>
+      <c r="G8" t="n">
+        <v>718</v>
+      </c>
+      <c r="H8" t="n">
+        <v>352.664</v>
+      </c>
+      <c r="I8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -1009,10 +1216,22 @@
       <c r="D9" t="n">
         <v>31.1173</v>
       </c>
-      <c r="E9" t="b">
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>357</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1078</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3205.0836</v>
+      </c>
+      <c r="I9" t="b">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -1031,10 +1250,22 @@
       <c r="D10" t="n">
         <v>25.8527</v>
       </c>
-      <c r="E10" t="b">
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" t="n">
+        <v>940</v>
+      </c>
+      <c r="H10" t="n">
+        <v>568.7595</v>
+      </c>
+      <c r="I10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -1053,10 +1284,22 @@
       <c r="D11" t="n">
         <v>25.0376</v>
       </c>
-      <c r="E11" t="b">
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>288</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1033</v>
+      </c>
+      <c r="H11" t="n">
+        <v>826.2397</v>
+      </c>
+      <c r="I11" t="b">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -1075,10 +1318,22 @@
       <c r="D12" t="n">
         <v>28.96</v>
       </c>
-      <c r="E12" t="b">
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>336</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1082</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2635.3587</v>
+      </c>
+      <c r="I12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>px</t>
         </is>
@@ -1097,10 +1352,22 @@
       <c r="D13" t="n">
         <v>27.013</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>245</v>
+      </c>
+      <c r="G13" t="n">
+        <v>877</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1782.8591</v>
+      </c>
+      <c r="I13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>px</t>
         </is>
